--- a/activity/M01A14/M01A14_DisenoVerticalPrototipo.xlsx
+++ b/activity/M01A14/M01A14_DisenoVerticalPrototipo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A14\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB663156-F59C-48D0-8A5D-2E92074B6D6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB92A735-B5E2-4447-8EFD-7A14ED63D84F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -518,7 +518,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -603,12 +603,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -651,6 +645,12 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -674,12 +674,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -796,7 +790,9 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="bg2"/>
+              <a:schemeClr val="bg1">
+                <a:lumMod val="85000"/>
+              </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2102,20 +2098,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
@@ -2145,7 +2141,7 @@
         <f>Detalle!C21*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="30"/>
+      <c r="E5" s="28"/>
       <c r="F5" s="25">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2162,7 +2158,7 @@
         <f>Detalle!F21*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="30"/>
+      <c r="E6" s="28"/>
       <c r="F6" s="25">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2179,7 +2175,7 @@
         <f>Detalle!I21*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="30"/>
+      <c r="E7" s="28"/>
       <c r="F7" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2196,7 +2192,7 @@
         <f>Detalle!L21*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="30"/>
+      <c r="E8" s="28"/>
       <c r="F8" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2213,7 +2209,7 @@
         <f>Detalle!O21*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="30"/>
+      <c r="E9" s="28"/>
       <c r="F9" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2230,7 +2226,7 @@
         <f>Detalle!R21*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="30"/>
+      <c r="E10" s="28"/>
       <c r="F10" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2247,7 +2243,7 @@
         <f>Detalle!U21*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="30"/>
+      <c r="E11" s="28"/>
       <c r="F11" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2264,7 +2260,7 @@
         <f>Detalle!X21*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="30"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2281,7 +2277,7 @@
         <f>Detalle!AA21*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="30"/>
+      <c r="E13" s="28"/>
       <c r="F13" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2298,7 +2294,7 @@
         <f>Detalle!AD21*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="30"/>
+      <c r="E14" s="28"/>
       <c r="F14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2315,7 +2311,7 @@
         <f>Detalle!AG21*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="30"/>
+      <c r="E15" s="28"/>
       <c r="F15" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2332,7 +2328,7 @@
         <f>Detalle!AJ21*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="30"/>
+      <c r="E16" s="28"/>
       <c r="F16" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2349,7 +2345,7 @@
         <f>Detalle!AM21*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="30"/>
+      <c r="E17" s="28"/>
       <c r="F17" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2366,7 +2362,7 @@
         <f>Detalle!AP21*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="31"/>
+      <c r="E18" s="29"/>
       <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2721,826 +2717,826 @@
       <c r="B4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="35"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="35"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="35"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="34"/>
-      <c r="AH4" s="35"/>
-      <c r="AI4" s="36"/>
-      <c r="AJ4" s="34"/>
-      <c r="AK4" s="35"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="34"/>
-      <c r="AN4" s="35"/>
-      <c r="AO4" s="36"/>
-      <c r="AP4" s="34"/>
-      <c r="AQ4" s="35"/>
-      <c r="AR4" s="36"/>
+      <c r="C4" s="32"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="34"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="34"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="34"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="33"/>
+      <c r="AI4" s="34"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="34"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="33"/>
+      <c r="AO4" s="34"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="33"/>
+      <c r="AR4" s="34"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B5" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="34">
-        <v>0</v>
-      </c>
-      <c r="D5" s="37"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="34">
-        <v>0</v>
-      </c>
-      <c r="G5" s="37"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="34">
-        <v>0</v>
-      </c>
-      <c r="J5" s="37"/>
-      <c r="K5" s="38"/>
-      <c r="L5" s="34">
-        <v>0</v>
-      </c>
-      <c r="M5" s="37"/>
-      <c r="N5" s="38"/>
-      <c r="O5" s="34">
-        <v>0</v>
-      </c>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="38"/>
-      <c r="R5" s="34">
-        <v>0</v>
-      </c>
-      <c r="S5" s="37"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="34">
-        <v>0</v>
-      </c>
-      <c r="V5" s="37"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="34">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="38"/>
-      <c r="AA5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="38"/>
-      <c r="AD5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="37"/>
-      <c r="AF5" s="38"/>
-      <c r="AG5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="37"/>
-      <c r="AL5" s="38"/>
-      <c r="AM5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AN5" s="37"/>
-      <c r="AO5" s="38"/>
-      <c r="AP5" s="34">
-        <v>0</v>
-      </c>
-      <c r="AQ5" s="37"/>
-      <c r="AR5" s="38"/>
+      <c r="C5" s="32">
+        <v>0</v>
+      </c>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="32">
+        <v>0</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="32">
+        <v>0</v>
+      </c>
+      <c r="J5" s="35"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="32">
+        <v>0</v>
+      </c>
+      <c r="M5" s="35"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="32">
+        <v>0</v>
+      </c>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="32">
+        <v>0</v>
+      </c>
+      <c r="S5" s="35"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="32">
+        <v>0</v>
+      </c>
+      <c r="V5" s="35"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="32">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="35"/>
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="35"/>
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="35"/>
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="35"/>
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="35"/>
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="32">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="35"/>
+      <c r="AR5" s="36"/>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="38"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="38"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="38"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="38"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="34"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="38"/>
-      <c r="AA6" s="34"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="38"/>
-      <c r="AD6" s="34"/>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="34"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="38"/>
-      <c r="AJ6" s="34"/>
-      <c r="AK6" s="37"/>
-      <c r="AL6" s="38"/>
-      <c r="AM6" s="34"/>
-      <c r="AN6" s="37"/>
-      <c r="AO6" s="38"/>
-      <c r="AP6" s="34"/>
-      <c r="AQ6" s="37"/>
-      <c r="AR6" s="38"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="32"/>
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="35"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="32"/>
+      <c r="AE6" s="35"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="32"/>
+      <c r="AH6" s="35"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="32"/>
+      <c r="AK6" s="35"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="32"/>
+      <c r="AN6" s="35"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="32"/>
+      <c r="AQ6" s="35"/>
+      <c r="AR6" s="36"/>
     </row>
     <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="37"/>
-      <c r="K7" s="38"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="38"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="34"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="38"/>
-      <c r="AA7" s="34"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="38"/>
-      <c r="AD7" s="34"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="38"/>
-      <c r="AG7" s="34"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="34"/>
-      <c r="AK7" s="37"/>
-      <c r="AL7" s="38"/>
-      <c r="AM7" s="34"/>
-      <c r="AN7" s="37"/>
-      <c r="AO7" s="38"/>
-      <c r="AP7" s="34"/>
-      <c r="AQ7" s="37"/>
-      <c r="AR7" s="38"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="32"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="32"/>
+      <c r="Y7" s="35"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="32"/>
+      <c r="AB7" s="35"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="32"/>
+      <c r="AE7" s="35"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="32"/>
+      <c r="AH7" s="35"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="32"/>
+      <c r="AK7" s="35"/>
+      <c r="AL7" s="36"/>
+      <c r="AM7" s="32"/>
+      <c r="AN7" s="35"/>
+      <c r="AO7" s="36"/>
+      <c r="AP7" s="32"/>
+      <c r="AQ7" s="35"/>
+      <c r="AR7" s="36"/>
     </row>
     <row r="8" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="38"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="34"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="38"/>
-      <c r="AA8" s="34"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="38"/>
-      <c r="AD8" s="34"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="38"/>
-      <c r="AG8" s="34"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="34"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="38"/>
-      <c r="AM8" s="34"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="38"/>
-      <c r="AP8" s="34"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="38"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="35"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="35"/>
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="35"/>
+      <c r="AF8" s="36"/>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="35"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="32"/>
+      <c r="AK8" s="35"/>
+      <c r="AL8" s="36"/>
+      <c r="AM8" s="32"/>
+      <c r="AN8" s="35"/>
+      <c r="AO8" s="36"/>
+      <c r="AP8" s="32"/>
+      <c r="AQ8" s="35"/>
+      <c r="AR8" s="36"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="13"/>
-      <c r="C9" s="34"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="38"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="34"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="38"/>
-      <c r="AA9" s="34"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="38"/>
-      <c r="AD9" s="34"/>
-      <c r="AE9" s="37"/>
-      <c r="AF9" s="38"/>
-      <c r="AG9" s="34"/>
-      <c r="AH9" s="37"/>
-      <c r="AI9" s="38"/>
-      <c r="AJ9" s="34"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="38"/>
-      <c r="AM9" s="34"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="38"/>
-      <c r="AP9" s="34"/>
-      <c r="AQ9" s="37"/>
-      <c r="AR9" s="38"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="35"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="35"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="32"/>
+      <c r="AK9" s="35"/>
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="32"/>
+      <c r="AN9" s="35"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="32"/>
+      <c r="AQ9" s="35"/>
+      <c r="AR9" s="36"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B10" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="34"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="36"/>
-      <c r="AA10" s="34"/>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="36"/>
-      <c r="AD10" s="34"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="36"/>
-      <c r="AG10" s="34"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="36"/>
-      <c r="AJ10" s="34"/>
-      <c r="AK10" s="35"/>
-      <c r="AL10" s="36"/>
-      <c r="AM10" s="34"/>
-      <c r="AN10" s="35"/>
-      <c r="AO10" s="36"/>
-      <c r="AP10" s="34"/>
-      <c r="AQ10" s="35"/>
-      <c r="AR10" s="36"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="32"/>
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="34"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="34"/>
+      <c r="AD10" s="32"/>
+      <c r="AE10" s="33"/>
+      <c r="AF10" s="34"/>
+      <c r="AG10" s="32"/>
+      <c r="AH10" s="33"/>
+      <c r="AI10" s="34"/>
+      <c r="AJ10" s="32"/>
+      <c r="AK10" s="33"/>
+      <c r="AL10" s="34"/>
+      <c r="AM10" s="32"/>
+      <c r="AN10" s="33"/>
+      <c r="AO10" s="34"/>
+      <c r="AP10" s="32"/>
+      <c r="AQ10" s="33"/>
+      <c r="AR10" s="34"/>
     </row>
     <row r="11" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B11" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="38"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="37"/>
-      <c r="K11" s="38"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="37"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="34"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="38"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="38"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="38"/>
-      <c r="AA11" s="34"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="38"/>
-      <c r="AD11" s="34"/>
-      <c r="AE11" s="37"/>
-      <c r="AF11" s="38"/>
-      <c r="AG11" s="34"/>
-      <c r="AH11" s="37"/>
-      <c r="AI11" s="38"/>
-      <c r="AJ11" s="34"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="38"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="38"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="37"/>
-      <c r="AR11" s="38"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="32"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="32"/>
+      <c r="AB11" s="35"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="32"/>
+      <c r="AE11" s="35"/>
+      <c r="AF11" s="36"/>
+      <c r="AG11" s="32"/>
+      <c r="AH11" s="35"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="32"/>
+      <c r="AK11" s="35"/>
+      <c r="AL11" s="36"/>
+      <c r="AM11" s="32"/>
+      <c r="AN11" s="35"/>
+      <c r="AO11" s="36"/>
+      <c r="AP11" s="32"/>
+      <c r="AQ11" s="35"/>
+      <c r="AR11" s="36"/>
     </row>
     <row r="12" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C12" s="34"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="34"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="37"/>
-      <c r="K12" s="38"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="37"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="34"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="38"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="38"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="34"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="38"/>
-      <c r="AA12" s="34"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="38"/>
-      <c r="AD12" s="34"/>
-      <c r="AE12" s="37"/>
-      <c r="AF12" s="38"/>
-      <c r="AG12" s="34"/>
-      <c r="AH12" s="37"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="34"/>
-      <c r="AK12" s="37"/>
-      <c r="AL12" s="38"/>
-      <c r="AM12" s="34"/>
-      <c r="AN12" s="37"/>
-      <c r="AO12" s="38"/>
-      <c r="AP12" s="34"/>
-      <c r="AQ12" s="37"/>
-      <c r="AR12" s="38"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="35"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="35"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="32"/>
+      <c r="AB12" s="35"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="32"/>
+      <c r="AE12" s="35"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="32"/>
+      <c r="AH12" s="35"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="32"/>
+      <c r="AK12" s="35"/>
+      <c r="AL12" s="36"/>
+      <c r="AM12" s="32"/>
+      <c r="AN12" s="35"/>
+      <c r="AO12" s="36"/>
+      <c r="AP12" s="32"/>
+      <c r="AQ12" s="35"/>
+      <c r="AR12" s="36"/>
     </row>
     <row r="13" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B13" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="37"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="38"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="34"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="38"/>
-      <c r="AA13" s="34"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="38"/>
-      <c r="AD13" s="34"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="38"/>
-      <c r="AG13" s="34"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="38"/>
-      <c r="AJ13" s="34"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="38"/>
-      <c r="AM13" s="34"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="38"/>
-      <c r="AP13" s="34"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="38"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="32"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="32"/>
+      <c r="AE13" s="35"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="32"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="32"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="32"/>
+      <c r="AN13" s="35"/>
+      <c r="AO13" s="36"/>
+      <c r="AP13" s="32"/>
+      <c r="AQ13" s="35"/>
+      <c r="AR13" s="36"/>
     </row>
     <row r="14" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B14" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="38"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="37"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="38"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="38"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="34"/>
-      <c r="Y14" s="37"/>
-      <c r="Z14" s="38"/>
-      <c r="AA14" s="34"/>
-      <c r="AB14" s="37"/>
-      <c r="AC14" s="38"/>
-      <c r="AD14" s="34"/>
-      <c r="AE14" s="37"/>
-      <c r="AF14" s="38"/>
-      <c r="AG14" s="34"/>
-      <c r="AH14" s="37"/>
-      <c r="AI14" s="38"/>
-      <c r="AJ14" s="34"/>
-      <c r="AK14" s="37"/>
-      <c r="AL14" s="38"/>
-      <c r="AM14" s="34"/>
-      <c r="AN14" s="37"/>
-      <c r="AO14" s="38"/>
-      <c r="AP14" s="34"/>
-      <c r="AQ14" s="37"/>
-      <c r="AR14" s="38"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="35"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="36"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="36"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="36"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="36"/>
+      <c r="X14" s="32"/>
+      <c r="Y14" s="35"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="32"/>
+      <c r="AB14" s="35"/>
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="32"/>
+      <c r="AE14" s="35"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="32"/>
+      <c r="AH14" s="35"/>
+      <c r="AI14" s="36"/>
+      <c r="AJ14" s="32"/>
+      <c r="AK14" s="35"/>
+      <c r="AL14" s="36"/>
+      <c r="AM14" s="32"/>
+      <c r="AN14" s="35"/>
+      <c r="AO14" s="36"/>
+      <c r="AP14" s="32"/>
+      <c r="AQ14" s="35"/>
+      <c r="AR14" s="36"/>
     </row>
     <row r="15" spans="1:44" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B15" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="38"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="38"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="38"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="37"/>
-      <c r="T15" s="38"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="37"/>
-      <c r="W15" s="38"/>
-      <c r="X15" s="34"/>
-      <c r="Y15" s="37"/>
-      <c r="Z15" s="38"/>
-      <c r="AA15" s="34"/>
-      <c r="AB15" s="37"/>
-      <c r="AC15" s="38"/>
-      <c r="AD15" s="34"/>
-      <c r="AE15" s="37"/>
-      <c r="AF15" s="38"/>
-      <c r="AG15" s="34"/>
-      <c r="AH15" s="37"/>
-      <c r="AI15" s="38"/>
-      <c r="AJ15" s="34"/>
-      <c r="AK15" s="37"/>
-      <c r="AL15" s="38"/>
-      <c r="AM15" s="34"/>
-      <c r="AN15" s="37"/>
-      <c r="AO15" s="38"/>
-      <c r="AP15" s="34"/>
-      <c r="AQ15" s="37"/>
-      <c r="AR15" s="38"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="35"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="32"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="32"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="32"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="32"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="32"/>
+      <c r="Y15" s="35"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="32"/>
+      <c r="AB15" s="35"/>
+      <c r="AC15" s="36"/>
+      <c r="AD15" s="32"/>
+      <c r="AE15" s="35"/>
+      <c r="AF15" s="36"/>
+      <c r="AG15" s="32"/>
+      <c r="AH15" s="35"/>
+      <c r="AI15" s="36"/>
+      <c r="AJ15" s="32"/>
+      <c r="AK15" s="35"/>
+      <c r="AL15" s="36"/>
+      <c r="AM15" s="32"/>
+      <c r="AN15" s="35"/>
+      <c r="AO15" s="36"/>
+      <c r="AP15" s="32"/>
+      <c r="AQ15" s="35"/>
+      <c r="AR15" s="36"/>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B16" s="13"/>
-      <c r="C16" s="34"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="38"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="38"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="38"/>
-      <c r="L16" s="34"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="38"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="38"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="38"/>
-      <c r="X16" s="34"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="38"/>
-      <c r="AA16" s="34"/>
-      <c r="AB16" s="37"/>
-      <c r="AC16" s="38"/>
-      <c r="AD16" s="34"/>
-      <c r="AE16" s="37"/>
-      <c r="AF16" s="38"/>
-      <c r="AG16" s="34"/>
-      <c r="AH16" s="37"/>
-      <c r="AI16" s="38"/>
-      <c r="AJ16" s="34"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="38"/>
-      <c r="AM16" s="34"/>
-      <c r="AN16" s="37"/>
-      <c r="AO16" s="38"/>
-      <c r="AP16" s="34"/>
-      <c r="AQ16" s="37"/>
-      <c r="AR16" s="38"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="32"/>
+      <c r="P16" s="35"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="32"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="35"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="32"/>
+      <c r="AB16" s="35"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="32"/>
+      <c r="AE16" s="35"/>
+      <c r="AF16" s="36"/>
+      <c r="AG16" s="32"/>
+      <c r="AH16" s="35"/>
+      <c r="AI16" s="36"/>
+      <c r="AJ16" s="32"/>
+      <c r="AK16" s="35"/>
+      <c r="AL16" s="36"/>
+      <c r="AM16" s="32"/>
+      <c r="AN16" s="35"/>
+      <c r="AO16" s="36"/>
+      <c r="AP16" s="32"/>
+      <c r="AQ16" s="35"/>
+      <c r="AR16" s="36"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="38"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="38"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="38"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="38"/>
-      <c r="X17" s="34"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="38"/>
-      <c r="AA17" s="34"/>
-      <c r="AB17" s="35"/>
-      <c r="AC17" s="38"/>
-      <c r="AD17" s="34"/>
-      <c r="AE17" s="35"/>
-      <c r="AF17" s="38"/>
-      <c r="AG17" s="34"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="38"/>
-      <c r="AJ17" s="34"/>
-      <c r="AK17" s="35"/>
-      <c r="AL17" s="38"/>
-      <c r="AM17" s="34"/>
-      <c r="AN17" s="35"/>
-      <c r="AO17" s="38"/>
-      <c r="AP17" s="34"/>
-      <c r="AQ17" s="35"/>
-      <c r="AR17" s="38"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="32"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="36"/>
+      <c r="AD17" s="32"/>
+      <c r="AE17" s="33"/>
+      <c r="AF17" s="36"/>
+      <c r="AG17" s="32"/>
+      <c r="AH17" s="33"/>
+      <c r="AI17" s="36"/>
+      <c r="AJ17" s="32"/>
+      <c r="AK17" s="33"/>
+      <c r="AL17" s="36"/>
+      <c r="AM17" s="32"/>
+      <c r="AN17" s="33"/>
+      <c r="AO17" s="36"/>
+      <c r="AP17" s="32"/>
+      <c r="AQ17" s="33"/>
+      <c r="AR17" s="36"/>
     </row>
     <row r="18" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="35"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="35"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="38"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="38"/>
-      <c r="X18" s="34"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="38"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="35"/>
-      <c r="AC18" s="38"/>
-      <c r="AD18" s="34"/>
-      <c r="AE18" s="35"/>
-      <c r="AF18" s="38"/>
-      <c r="AG18" s="34"/>
-      <c r="AH18" s="35"/>
-      <c r="AI18" s="38"/>
-      <c r="AJ18" s="34"/>
-      <c r="AK18" s="35"/>
-      <c r="AL18" s="38"/>
-      <c r="AM18" s="34"/>
-      <c r="AN18" s="35"/>
-      <c r="AO18" s="38"/>
-      <c r="AP18" s="34"/>
-      <c r="AQ18" s="35"/>
-      <c r="AR18" s="38"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="33"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="32"/>
+      <c r="AE18" s="33"/>
+      <c r="AF18" s="36"/>
+      <c r="AG18" s="32"/>
+      <c r="AH18" s="33"/>
+      <c r="AI18" s="36"/>
+      <c r="AJ18" s="32"/>
+      <c r="AK18" s="33"/>
+      <c r="AL18" s="36"/>
+      <c r="AM18" s="32"/>
+      <c r="AN18" s="33"/>
+      <c r="AO18" s="36"/>
+      <c r="AP18" s="32"/>
+      <c r="AQ18" s="33"/>
+      <c r="AR18" s="36"/>
     </row>
     <row r="19" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="35"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="38"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="38"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="38"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="38"/>
-      <c r="AA19" s="34"/>
-      <c r="AB19" s="35"/>
-      <c r="AC19" s="38"/>
-      <c r="AD19" s="34"/>
-      <c r="AE19" s="35"/>
-      <c r="AF19" s="38"/>
-      <c r="AG19" s="34"/>
-      <c r="AH19" s="35"/>
-      <c r="AI19" s="38"/>
-      <c r="AJ19" s="34"/>
-      <c r="AK19" s="35"/>
-      <c r="AL19" s="38"/>
-      <c r="AM19" s="34"/>
-      <c r="AN19" s="35"/>
-      <c r="AO19" s="38"/>
-      <c r="AP19" s="34"/>
-      <c r="AQ19" s="35"/>
-      <c r="AR19" s="38"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="32"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="32"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="32"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="32"/>
+      <c r="AB19" s="33"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="32"/>
+      <c r="AE19" s="33"/>
+      <c r="AF19" s="36"/>
+      <c r="AG19" s="32"/>
+      <c r="AH19" s="33"/>
+      <c r="AI19" s="36"/>
+      <c r="AJ19" s="32"/>
+      <c r="AK19" s="33"/>
+      <c r="AL19" s="36"/>
+      <c r="AM19" s="32"/>
+      <c r="AN19" s="33"/>
+      <c r="AO19" s="36"/>
+      <c r="AP19" s="32"/>
+      <c r="AQ19" s="33"/>
+      <c r="AR19" s="36"/>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B20" s="32"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="39"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="39"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="39"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="39"/>
-      <c r="S20" s="40"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="39"/>
-      <c r="V20" s="40"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="39"/>
-      <c r="Y20" s="40"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="39"/>
-      <c r="AB20" s="40"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="39"/>
-      <c r="AE20" s="40"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="39"/>
-      <c r="AH20" s="40"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="39"/>
-      <c r="AK20" s="40"/>
-      <c r="AL20" s="41"/>
-      <c r="AM20" s="39"/>
-      <c r="AN20" s="40"/>
-      <c r="AO20" s="41"/>
-      <c r="AP20" s="39"/>
-      <c r="AQ20" s="40"/>
-      <c r="AR20" s="41"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="38"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="37"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="37"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="37"/>
+      <c r="S20" s="38"/>
+      <c r="T20" s="39"/>
+      <c r="U20" s="37"/>
+      <c r="V20" s="38"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="37"/>
+      <c r="Y20" s="38"/>
+      <c r="Z20" s="39"/>
+      <c r="AA20" s="37"/>
+      <c r="AB20" s="38"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="37"/>
+      <c r="AE20" s="38"/>
+      <c r="AF20" s="39"/>
+      <c r="AG20" s="37"/>
+      <c r="AH20" s="38"/>
+      <c r="AI20" s="39"/>
+      <c r="AJ20" s="37"/>
+      <c r="AK20" s="38"/>
+      <c r="AL20" s="39"/>
+      <c r="AM20" s="37"/>
+      <c r="AN20" s="38"/>
+      <c r="AO20" s="39"/>
+      <c r="AP20" s="37"/>
+      <c r="AQ20" s="38"/>
+      <c r="AR20" s="39"/>
     </row>
     <row r="21" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
-      <c r="B21" s="33" t="s">
+      <c r="B21" s="31" t="s">
         <v>1</v>
       </c>
       <c r="C21" s="45">
